--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>alerta_reposicion</t>
+          <t>precio_unitario</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>valor_total_stock</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>estado</t>
         </is>
       </c>
     </row>
@@ -440,10 +450,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96</v>
-      </c>
-      <c r="C2" t="b">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="C2" t="n">
+        <v>889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32893</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -453,10 +471,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93</v>
-      </c>
-      <c r="C3" t="b">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="C3" t="n">
+        <v>666</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50616</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -466,49 +492,333 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1778</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17780</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tapas_empanada</t>
+          <t>jamon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99</v>
-      </c>
-      <c r="C5" t="b">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1630</v>
+      </c>
+      <c r="D5" t="n">
+        <v>156480</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>relleno_empanada</t>
+          <t>morron</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>75</v>
-      </c>
-      <c r="C6" t="b">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="C6" t="n">
+        <v>740</v>
+      </c>
+      <c r="D6" t="n">
+        <v>34780</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>cebolla</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="n">
+        <v>518</v>
+      </c>
+      <c r="D7" t="n">
+        <v>36260</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tomate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>41</v>
+      </c>
+      <c r="C8" t="n">
+        <v>666</v>
+      </c>
+      <c r="D8" t="n">
+        <v>27306</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ajo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C9" t="n">
+        <v>370</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19610</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>roquefort</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>68</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2222</v>
+      </c>
+      <c r="D10" t="n">
+        <v>151096</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aceitunas</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>67</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1037</v>
+      </c>
+      <c r="D11" t="n">
+        <v>69479</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tapas_empanada</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>73</v>
+      </c>
+      <c r="C12" t="n">
+        <v>296</v>
+      </c>
+      <c r="D12" t="n">
+        <v>21608</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>carne</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>85</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D13" t="n">
+        <v>125885</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>jamon_queso</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>54</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1407</v>
+      </c>
+      <c r="D14" t="n">
+        <v>75978</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pollo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>84</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D15" t="n">
+        <v>111972</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>verdura</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>71</v>
+      </c>
+      <c r="C16" t="n">
+        <v>889</v>
+      </c>
+      <c r="D16" t="n">
+        <v>63119</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>humita</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>55</v>
+      </c>
+      <c r="C17" t="n">
+        <v>815</v>
+      </c>
+      <c r="D17" t="n">
+        <v>44825</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>gaseosa</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>97</v>
-      </c>
-      <c r="C7" t="b">
-        <v>0</v>
+      <c r="B18" t="n">
+        <v>80</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D18" t="n">
+        <v>94800</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>agua</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>62</v>
+      </c>
+      <c r="C19" t="n">
+        <v>666</v>
+      </c>
+      <c r="D19" t="n">
+        <v>41292</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
         <v>889</v>
       </c>
       <c r="D2" t="n">
-        <v>32893</v>
+        <v>66675</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
         <v>666</v>
       </c>
       <c r="D3" t="n">
-        <v>50616</v>
+        <v>60606</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
         <v>1778</v>
       </c>
       <c r="D4" t="n">
-        <v>17780</v>
+        <v>128016</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C5" t="n">
         <v>1630</v>
       </c>
       <c r="D5" t="n">
-        <v>156480</v>
+        <v>140180</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="C6" t="n">
         <v>740</v>
       </c>
       <c r="D6" t="n">
-        <v>34780</v>
+        <v>68820</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
         <v>518</v>
       </c>
       <c r="D7" t="n">
-        <v>36260</v>
+        <v>28490</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -576,13 +576,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
         <v>666</v>
       </c>
       <c r="D8" t="n">
-        <v>27306</v>
+        <v>29304</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
         <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>19610</v>
+        <v>18870</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C10" t="n">
         <v>2222</v>
       </c>
       <c r="D10" t="n">
-        <v>151096</v>
+        <v>215534</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C11" t="n">
         <v>1037</v>
       </c>
       <c r="D11" t="n">
-        <v>69479</v>
+        <v>66368</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C12" t="n">
         <v>296</v>
       </c>
       <c r="D12" t="n">
-        <v>21608</v>
+        <v>29304</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C13" t="n">
         <v>1481</v>
       </c>
       <c r="D13" t="n">
-        <v>125885</v>
+        <v>118480</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C14" t="n">
         <v>1407</v>
       </c>
       <c r="D14" t="n">
-        <v>75978</v>
+        <v>95676</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C16" t="n">
         <v>889</v>
       </c>
       <c r="D16" t="n">
-        <v>63119</v>
+        <v>85344</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C17" t="n">
         <v>815</v>
       </c>
       <c r="D17" t="n">
-        <v>44825</v>
+        <v>72535</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C18" t="n">
         <v>1185</v>
       </c>
       <c r="D18" t="n">
-        <v>94800</v>
+        <v>111390</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C19" t="n">
         <v>666</v>
       </c>
       <c r="D19" t="n">
-        <v>41292</v>
+        <v>31302</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
         <v>889</v>
       </c>
       <c r="D2" t="n">
-        <v>66675</v>
+        <v>47117</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C3" t="n">
         <v>666</v>
       </c>
       <c r="D3" t="n">
-        <v>60606</v>
+        <v>40626</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>1778</v>
       </c>
       <c r="D4" t="n">
-        <v>128016</v>
+        <v>46228</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C5" t="n">
         <v>1630</v>
       </c>
       <c r="D5" t="n">
-        <v>140180</v>
+        <v>104320</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n">
         <v>740</v>
       </c>
       <c r="D6" t="n">
-        <v>68820</v>
+        <v>48840</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
         <v>518</v>
       </c>
       <c r="D7" t="n">
-        <v>28490</v>
+        <v>15540</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -576,13 +576,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
         <v>666</v>
       </c>
       <c r="D8" t="n">
-        <v>29304</v>
+        <v>24642</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
         <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>18870</v>
+        <v>24790</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
         <v>2222</v>
       </c>
       <c r="D10" t="n">
-        <v>215534</v>
+        <v>99990</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" t="n">
         <v>1037</v>
       </c>
       <c r="D11" t="n">
-        <v>66368</v>
+        <v>65331</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="C12" t="n">
         <v>296</v>
       </c>
       <c r="D12" t="n">
-        <v>29304</v>
+        <v>14208</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
         <v>1481</v>
       </c>
       <c r="D13" t="n">
-        <v>118480</v>
+        <v>74050</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
         <v>1407</v>
       </c>
       <c r="D14" t="n">
-        <v>95676</v>
+        <v>53466</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="C15" t="n">
         <v>1333</v>
       </c>
       <c r="D15" t="n">
-        <v>111972</v>
+        <v>41323</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="C16" t="n">
         <v>889</v>
       </c>
       <c r="D16" t="n">
-        <v>85344</v>
+        <v>43561</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C17" t="n">
         <v>815</v>
       </c>
       <c r="D17" t="n">
-        <v>72535</v>
+        <v>44825</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="C18" t="n">
         <v>1185</v>
       </c>
       <c r="D18" t="n">
-        <v>111390</v>
+        <v>61620</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C19" t="n">
         <v>666</v>
       </c>
       <c r="D19" t="n">
-        <v>31302</v>
+        <v>39294</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00111827"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +137,20 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaStock" displayName="TablaStock" ref="A1:E19" headerRowCount="1">
+  <autoFilter ref="A1:E19"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Ingrediente"/>
+    <tableColumn id="2" name="Cantidad"/>
+    <tableColumn id="3" name="Precio unitario"/>
+    <tableColumn id="4" name="Valor total"/>
+    <tableColumn id="5" name="Estado"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -415,407 +444,414 @@
   </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ingrediente</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>cantidad</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>precio_unitario</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>valor_total_stock</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>estado</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ingrediente</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Precio unitario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valor total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>aceitunas</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>45500</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>agua</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>17100</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ajo</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>carne</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>62000</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>cebolla</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>19600</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>gaseosa</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>39200</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>harina</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>53</v>
-      </c>
-      <c r="C2" t="n">
-        <v>889</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47117</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B8" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>37800</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>humita</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>29700</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>jamon</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>44000</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>jamon_queso</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>63650</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>morron</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>19500</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>mozzarella</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>54000</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>pollo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>49500</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>roquefort</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>salsa</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>61</v>
-      </c>
-      <c r="C3" t="n">
-        <v>666</v>
-      </c>
-      <c r="D3" t="n">
-        <v>40626</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mozzarella</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>26</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1778</v>
-      </c>
-      <c r="D4" t="n">
-        <v>46228</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>jamon</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>64</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1630</v>
-      </c>
-      <c r="D5" t="n">
-        <v>104320</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>morron</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>66</v>
-      </c>
-      <c r="C6" t="n">
-        <v>740</v>
-      </c>
-      <c r="D6" t="n">
-        <v>48840</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cebolla</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C7" t="n">
-        <v>518</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15540</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B16" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>22050</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>tapas_empanada</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>tomate</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>37</v>
-      </c>
-      <c r="C8" t="n">
-        <v>666</v>
-      </c>
-      <c r="D8" t="n">
-        <v>24642</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ajo</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>67</v>
-      </c>
-      <c r="C9" t="n">
-        <v>370</v>
-      </c>
-      <c r="D9" t="n">
-        <v>24790</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>roquefort</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>45</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2222</v>
-      </c>
-      <c r="D10" t="n">
-        <v>99990</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>aceitunas</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>63</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1037</v>
-      </c>
-      <c r="D11" t="n">
-        <v>65331</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tapas_empanada</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>48</v>
-      </c>
-      <c r="C12" t="n">
-        <v>296</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14208</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>carne</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>50</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="D13" t="n">
-        <v>74050</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>jamon_queso</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>38</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1407</v>
-      </c>
-      <c r="D14" t="n">
-        <v>53466</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>pollo</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>31</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1333</v>
-      </c>
-      <c r="D15" t="n">
-        <v>41323</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B18" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>24750</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>verdura</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>49</v>
-      </c>
-      <c r="C16" t="n">
-        <v>889</v>
-      </c>
-      <c r="D16" t="n">
-        <v>43561</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>humita</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>55</v>
-      </c>
-      <c r="C17" t="n">
-        <v>815</v>
-      </c>
-      <c r="D17" t="n">
-        <v>44825</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>gaseosa</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>52</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1185</v>
-      </c>
-      <c r="D18" t="n">
-        <v>61620</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>agua</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>59</v>
-      </c>
-      <c r="C19" t="n">
-        <v>666</v>
-      </c>
-      <c r="D19" t="n">
-        <v>39294</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="B19" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>25800</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Disponible</t>
         </is>
@@ -823,5 +859,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1050</v>
+        <v>1037</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45150</v>
+        <v>66368</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32400</v>
+        <v>39294</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>23625</v>
+        <v>12950</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1500</v>
+        <v>1481</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>94500</v>
+        <v>51835</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>28875</v>
+        <v>25900</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>74400</v>
+        <v>71100</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>900</v>
+        <v>889</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>35100</v>
+        <v>33782</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>30525</v>
+        <v>56980</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1650</v>
+        <v>1629</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>64350</v>
+        <v>55386</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1425</v>
+        <v>1407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>84075</v>
+        <v>75978</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>40500</v>
+        <v>42920</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1800</v>
+        <v>1778</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>122400</v>
+        <v>58674</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1350</v>
+        <v>1333</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>75600</v>
+        <v>59985</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2250</v>
+        <v>2222</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>74250</v>
+        <v>119988</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>21600</v>
+        <v>34632</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>15300</v>
+        <v>17168</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>28350</v>
+        <v>31302</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>900</v>
+        <v>889</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>39600</v>
+        <v>62230</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1037</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>66368</v>
+        <v>45628</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>666</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>39294</v>
+        <v>31968</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>370</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12950</v>
+        <v>22940</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>1481</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>51835</v>
+        <v>77012</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>518</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25900</v>
+        <v>25382</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>1185</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>71100</v>
+        <v>50955</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>889</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>33782</v>
+        <v>54229</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>814</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>56980</v>
+        <v>43956</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1629</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>55386</v>
+        <v>76563</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>1407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>75978</v>
+        <v>98490</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>740</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>42920</v>
+        <v>23680</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1778</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>58674</v>
+        <v>78232</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>1333</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>59985</v>
+        <v>89311</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>2222</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>119988</v>
+        <v>153318</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>666</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34632</v>
+        <v>42624</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>296</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>17168</v>
+        <v>13320</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>666</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>31302</v>
+        <v>37962</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>889</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>62230</v>
+        <v>45339</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -445,7 +445,7 @@
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -482,17 +482,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>aceitunas</t>
+          <t>Aceitunas</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45628</v>
+        <v>62580</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>Agua</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>31968</v>
+        <v>28140</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -524,17 +524,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ajo</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>22940</v>
+        <v>15252</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -545,17 +545,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>carne</t>
+          <t>Carne</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1481</v>
+        <v>1490</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>77012</v>
+        <v>58110</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -566,17 +566,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>cebolla</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25382</v>
+        <v>30739</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -587,17 +587,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>gaseosa</t>
+          <t>Gaseosa</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>50955</v>
+        <v>60792</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -608,17 +608,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>harina</t>
+          <t>Harina</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>54229</v>
+        <v>22350</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -629,17 +629,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>humita</t>
+          <t>Humita</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>43956</v>
+        <v>40131</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -650,17 +650,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>jamon</t>
+          <t>Jamón</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1629</v>
+        <v>1639</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>76563</v>
+        <v>113091</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -671,17 +671,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>jamon_queso</t>
+          <t>Jamón y queso</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>98490</v>
+        <v>48110</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -692,17 +692,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>morron</t>
+          <t>Morrón</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>23680</v>
+        <v>49170</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>mozzarella</t>
+          <t>Mozzarella</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1778</v>
+        <v>1788</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>78232</v>
+        <v>62580</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>pollo</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>89311</v>
+        <v>46935</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -755,17 +755,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>roquefort</t>
+          <t>Roquefort</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2222</v>
+        <v>2235</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>153318</v>
+        <v>31290</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -776,17 +776,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>salsa</t>
+          <t>Salsa</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>42624</v>
+        <v>33500</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -797,17 +797,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tapas_empanada</t>
+          <t>Tapas de empanada</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>13320</v>
+        <v>7450</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -818,17 +818,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>tomate</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>37962</v>
+        <v>28810</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -839,17 +839,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>verdura</t>
+          <t>Verdura</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45339</v>
+        <v>56322</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1043</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>62580</v>
+        <v>56322</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>670</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>28140</v>
+        <v>30150</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>372</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>15252</v>
+        <v>19344</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>1490</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>58110</v>
+        <v>96850</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>521</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30739</v>
+        <v>33865</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>1192</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>60792</v>
+        <v>63176</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>894</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>22350</v>
+        <v>31290</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>819</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>40131</v>
+        <v>44226</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1639</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>113091</v>
+        <v>95062</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>1415</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>48110</v>
+        <v>97635</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>745</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>49170</v>
+        <v>30545</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1788</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>62580</v>
+        <v>114432</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>1341</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46935</v>
+        <v>61686</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>2235</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>31290</v>
+        <v>118455</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>670</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>33500</v>
+        <v>44220</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>298</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7450</v>
+        <v>19668</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>670</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>28810</v>
+        <v>22780</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>894</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>56322</v>
+        <v>59898</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1043</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>56322</v>
+        <v>58408</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>670</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>30150</v>
+        <v>21440</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>372</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>19344</v>
+        <v>13764</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>1490</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>96850</v>
+        <v>73010</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>521</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>33865</v>
+        <v>19798</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>1192</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>63176</v>
+        <v>78672</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>894</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>31290</v>
+        <v>54534</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>819</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>44226</v>
+        <v>40950</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1639</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>95062</v>
+        <v>93423</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>1415</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>97635</v>
+        <v>69335</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>745</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>30545</v>
+        <v>42465</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1788</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>114432</v>
+        <v>75096</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>1341</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>61686</v>
+        <v>42912</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>2235</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>118455</v>
+        <v>69285</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>670</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>44220</v>
+        <v>24790</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>298</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>19668</v>
+        <v>15198</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>670</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>22780</v>
+        <v>26130</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>894</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>59898</v>
+        <v>38442</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -489,10 +489,10 @@
         <v>56</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>58408</v>
+        <v>58576</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>21440</v>
+        <v>21504</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -531,10 +531,10 @@
         <v>37</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13764</v>
+        <v>13801</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -552,10 +552,10 @@
         <v>49</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1490</v>
+        <v>1495</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>73010</v>
+        <v>73255</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         <v>38</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>19798</v>
+        <v>19874</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         <v>66</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>78672</v>
+        <v>78936</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -615,10 +615,10 @@
         <v>61</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>54534</v>
+        <v>54717</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         <v>50</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>40950</v>
+        <v>41100</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -657,10 +657,10 @@
         <v>57</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1639</v>
+        <v>1644</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>93423</v>
+        <v>93708</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>49</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1415</v>
+        <v>1420</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>69335</v>
+        <v>69580</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         <v>57</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>42465</v>
+        <v>42579</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>42</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1788</v>
+        <v>1794</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>75096</v>
+        <v>75348</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -741,10 +741,10 @@
         <v>32</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>42912</v>
+        <v>43040</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2235</v>
+        <v>2242</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>69285</v>
+        <v>69502</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -783,10 +783,10 @@
         <v>37</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24790</v>
+        <v>24864</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         <v>51</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>15198</v>
+        <v>15249</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         <v>39</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>26130</v>
+        <v>26208</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -846,10 +846,10 @@
         <v>43</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>38442</v>
+        <v>38571</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>

--- a/reportes/reporte_stock.xlsx
+++ b/reportes/reporte_stock.xlsx
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1046</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>58576</v>
+        <v>71128</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>672</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>21504</v>
+        <v>27552</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>373</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13801</v>
+        <v>20888</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>1495</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>73255</v>
+        <v>94185</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>523</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>19874</v>
+        <v>34518</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>1196</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>78936</v>
+        <v>74152</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>897</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>54717</v>
+        <v>37674</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>822</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>41100</v>
+        <v>48498</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1644</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>93708</v>
+        <v>115080</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>1420</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>69580</v>
+        <v>42600</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>747</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>42579</v>
+        <v>46314</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1794</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>75348</v>
+        <v>73554</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>1345</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>43040</v>
+        <v>94150</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>2242</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>69502</v>
+        <v>114342</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>672</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24864</v>
+        <v>24192</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>299</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>15249</v>
+        <v>11661</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>672</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>26208</v>
+        <v>31584</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>897</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>38571</v>
+        <v>27807</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
